--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131136818</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131136808</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131136961</v>
+        <v>131136874</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,27 +906,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789068</v>
+        <v>788960</v>
       </c>
       <c r="R4" t="n">
-        <v>7131245</v>
+        <v>7131416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,17 +975,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,7 +1003,7 @@
         <v>131136941</v>
       </c>
       <c r="B5" t="n">
-        <v>83091</v>
+        <v>83092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131136874</v>
+        <v>131136961</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,30 +1121,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788960</v>
+        <v>789068</v>
       </c>
       <c r="R6" t="n">
-        <v>7131416</v>
+        <v>7131245</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,13 +1187,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>131136881</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>131136918</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131136813</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>131136774</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131136826</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131136930</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131136896</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>131136854</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>131136788</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>131136785</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131136818</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131136808</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131136874</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131136941</v>
       </c>
       <c r="B5" t="n">
-        <v>83092</v>
+        <v>83094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131136961</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131136881</v>
+        <v>131136984</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,30 +1227,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788972</v>
+        <v>788839</v>
       </c>
       <c r="R7" t="n">
-        <v>7131396</v>
+        <v>7131504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,13 +1297,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hål i tallstam</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131136984</v>
+        <v>131136881</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,31 +1337,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788839</v>
+        <v>788972</v>
       </c>
       <c r="R8" t="n">
-        <v>7131504</v>
+        <v>7131396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,17 +1406,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hål i tallstam</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>131136918</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131136813</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>131136774</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131136826</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131136930</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131136896</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>131136854</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>131136788</v>
       </c>
       <c r="B16" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>131136785</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131136818</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131136808</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131136874</v>
+        <v>131136941</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>83095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,27 +906,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788960</v>
+        <v>788995</v>
       </c>
       <c r="R4" t="n">
-        <v>7131416</v>
+        <v>7131220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131136941</v>
+        <v>131136874</v>
       </c>
       <c r="B5" t="n">
-        <v>83094</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,27 +1016,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1042,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788995</v>
+        <v>788960</v>
       </c>
       <c r="R5" t="n">
-        <v>7131220</v>
+        <v>7131416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,11 +1083,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1113,7 @@
         <v>131136961</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>131136984</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>131136881</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>131136918</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131136813</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>131136774</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131136826</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131136930</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131136896</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>131136854</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>131136788</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>131136785</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131136941</v>
+        <v>131136874</v>
       </c>
       <c r="B4" t="n">
-        <v>83095</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,27 +906,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788995</v>
+        <v>788960</v>
       </c>
       <c r="R4" t="n">
-        <v>7131220</v>
+        <v>7131416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131136874</v>
+        <v>131136941</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>83095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,27 +1011,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1047,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788960</v>
+        <v>788995</v>
       </c>
       <c r="R5" t="n">
-        <v>7131416</v>
+        <v>7131220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131136813</v>
+        <v>131136826</v>
       </c>
       <c r="B10" t="n">
         <v>79249</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788939</v>
+        <v>788924</v>
       </c>
       <c r="R10" t="n">
-        <v>7131477</v>
+        <v>7131449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131136774</v>
+        <v>131136813</v>
       </c>
       <c r="B11" t="n">
         <v>79249</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>788847</v>
+        <v>788939</v>
       </c>
       <c r="R11" t="n">
-        <v>7131680</v>
+        <v>7131477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131136826</v>
+        <v>131136774</v>
       </c>
       <c r="B12" t="n">
         <v>79249</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788924</v>
+        <v>788847</v>
       </c>
       <c r="R12" t="n">
-        <v>7131449</v>
+        <v>7131680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131136874</v>
+        <v>131136941</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>83095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,27 +906,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788960</v>
+        <v>788995</v>
       </c>
       <c r="R4" t="n">
-        <v>7131416</v>
+        <v>7131220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131136941</v>
+        <v>131136874</v>
       </c>
       <c r="B5" t="n">
-        <v>83095</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,27 +1016,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1042,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788995</v>
+        <v>788960</v>
       </c>
       <c r="R5" t="n">
-        <v>7131220</v>
+        <v>7131416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,11 +1083,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131136984</v>
+        <v>131136881</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,31 +1227,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788839</v>
+        <v>788972</v>
       </c>
       <c r="R7" t="n">
-        <v>7131504</v>
+        <v>7131396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,17 +1296,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hål i tallstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1326,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131136881</v>
+        <v>131136984</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,30 +1332,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788972</v>
+        <v>788839</v>
       </c>
       <c r="R8" t="n">
-        <v>7131396</v>
+        <v>7131504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,13 +1402,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hål i tallstam</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131136826</v>
+        <v>131136813</v>
       </c>
       <c r="B10" t="n">
         <v>79249</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788924</v>
+        <v>788939</v>
       </c>
       <c r="R10" t="n">
-        <v>7131449</v>
+        <v>7131477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131136813</v>
+        <v>131136774</v>
       </c>
       <c r="B11" t="n">
         <v>79249</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>788939</v>
+        <v>788847</v>
       </c>
       <c r="R11" t="n">
-        <v>7131477</v>
+        <v>7131680</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131136774</v>
+        <v>131136826</v>
       </c>
       <c r="B12" t="n">
         <v>79249</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788847</v>
+        <v>788924</v>
       </c>
       <c r="R12" t="n">
-        <v>7131680</v>
+        <v>7131449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131136818</v>
+        <v>131136808</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788933</v>
+        <v>788922</v>
       </c>
       <c r="R2" t="n">
-        <v>7131460</v>
+        <v>7131486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ca 0,4 m lång bål</t>
+          <t>på tallstam</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131136808</v>
+        <v>131136818</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788922</v>
+        <v>788933</v>
       </c>
       <c r="R3" t="n">
-        <v>7131486</v>
+        <v>7131460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på tallstam</t>
+          <t>ca 0,4 m lång bål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +898,7 @@
         <v>131136941</v>
       </c>
       <c r="B4" t="n">
-        <v>83095</v>
+        <v>83096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>131136874</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131136961</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131136881</v>
+        <v>131136984</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,30 +1227,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788972</v>
+        <v>788839</v>
       </c>
       <c r="R7" t="n">
-        <v>7131396</v>
+        <v>7131504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,13 +1297,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hål i tallstam</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131136984</v>
+        <v>131136881</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,31 +1337,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788839</v>
+        <v>788972</v>
       </c>
       <c r="R8" t="n">
-        <v>7131504</v>
+        <v>7131396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,17 +1406,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hål i tallstam</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>131136918</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131136813</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>131136774</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131136826</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131136930</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131136896</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>131136854</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>131136788</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>131136785</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131136808</v>
+        <v>131136818</v>
       </c>
       <c r="B2" t="n">
         <v>79250</v>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788922</v>
+        <v>788933</v>
       </c>
       <c r="R2" t="n">
-        <v>7131486</v>
+        <v>7131460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på tallstam</t>
+          <t>ca 0,4 m lång bål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131136818</v>
+        <v>131136808</v>
       </c>
       <c r="B3" t="n">
         <v>79250</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788933</v>
+        <v>788922</v>
       </c>
       <c r="R3" t="n">
-        <v>7131460</v>
+        <v>7131486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ca 0,4 m lång bål</t>
+          <t>på tallstam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131136941</v>
+        <v>131136874</v>
       </c>
       <c r="B4" t="n">
-        <v>83096</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,27 +906,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788995</v>
+        <v>788960</v>
       </c>
       <c r="R4" t="n">
-        <v>7131220</v>
+        <v>7131416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131136874</v>
+        <v>131136941</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>83096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,27 +1011,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1047,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788960</v>
+        <v>788995</v>
       </c>
       <c r="R5" t="n">
-        <v>7131416</v>
+        <v>7131220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131136984</v>
+        <v>131136881</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,31 +1227,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788839</v>
+        <v>788972</v>
       </c>
       <c r="R7" t="n">
-        <v>7131504</v>
+        <v>7131396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,17 +1296,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hål i tallstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1326,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131136881</v>
+        <v>131136984</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,30 +1332,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788972</v>
+        <v>788839</v>
       </c>
       <c r="R8" t="n">
-        <v>7131396</v>
+        <v>7131504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,13 +1402,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hål i tallstam</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131136818</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131136808</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131136874</v>
+        <v>131136941</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>83099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,27 +906,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788960</v>
+        <v>788995</v>
       </c>
       <c r="R4" t="n">
-        <v>7131416</v>
+        <v>7131220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131136941</v>
+        <v>131136874</v>
       </c>
       <c r="B5" t="n">
-        <v>83096</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,27 +1016,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1042,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788995</v>
+        <v>788960</v>
       </c>
       <c r="R5" t="n">
-        <v>7131220</v>
+        <v>7131416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,11 +1083,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1113,7 @@
         <v>131136961</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>131136881</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>131136984</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>131136918</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131136813</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>131136774</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131136826</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131136930</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131136896</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>131136854</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>131136788</v>
       </c>
       <c r="B16" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>131136785</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131136818</v>
       </c>
       <c r="B2" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131136808</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131136941</v>
+        <v>131136874</v>
       </c>
       <c r="B4" t="n">
-        <v>83099</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,27 +906,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788995</v>
+        <v>788960</v>
       </c>
       <c r="R4" t="n">
-        <v>7131220</v>
+        <v>7131416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131136874</v>
+        <v>131136961</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,30 +1011,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788960</v>
+        <v>789068</v>
       </c>
       <c r="R5" t="n">
-        <v>7131416</v>
+        <v>7131245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,13 +1077,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131136961</v>
+        <v>131136941</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>83100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,27 +1117,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789068</v>
+        <v>788995</v>
       </c>
       <c r="R6" t="n">
-        <v>7131245</v>
+        <v>7131220</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,15 +1188,16 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>på en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>131136881</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>131136984</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>131136918</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131136813</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>131136774</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131136826</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131136930</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131136896</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>131136854</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>131136788</v>
       </c>
       <c r="B16" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>131136785</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131136881</v>
+        <v>131136984</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,30 +1227,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788972</v>
+        <v>788839</v>
       </c>
       <c r="R7" t="n">
-        <v>7131396</v>
+        <v>7131504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,13 +1297,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hål i tallstam</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131136984</v>
+        <v>131136881</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,31 +1337,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788839</v>
+        <v>788972</v>
       </c>
       <c r="R8" t="n">
-        <v>7131504</v>
+        <v>7131396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,17 +1406,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hål i tallstam</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131136818</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131136808</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131136874</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131136961</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>131136941</v>
       </c>
       <c r="B6" t="n">
-        <v>83100</v>
+        <v>83106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131136984</v>
+        <v>131136881</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,31 +1227,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788839</v>
+        <v>788972</v>
       </c>
       <c r="R7" t="n">
-        <v>7131504</v>
+        <v>7131396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,17 +1296,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hål i tallstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1326,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131136881</v>
+        <v>131136984</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,30 +1332,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788972</v>
+        <v>788839</v>
       </c>
       <c r="R8" t="n">
-        <v>7131396</v>
+        <v>7131504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,13 +1402,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hål i tallstam</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>131136918</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131136813</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>131136774</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131136826</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131136930</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131136896</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>131136854</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>131136788</v>
       </c>
       <c r="B16" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>131136785</v>
       </c>
       <c r="B17" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 5292-2026 artfynd.xlsx
+++ b/artfynd/A 5292-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136774</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136785</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136813</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136818</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136826</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136854</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136874</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,6 +1907,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136881</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1962,6 +2022,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136896</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136918</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,6 +2242,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136930</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136984</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2388,8 +2468,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136961</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>